--- a/loan_application_forms/033_mortgage_approval_validation_form--loan_application_forms.xlsx
+++ b/loan_application_forms/033_mortgage_approval_validation_form--loan_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Self Employed'}</t>
+          <t>Self Employed</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1-5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1-5 years'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'10-15_years'}</t>
+          <t>10-15_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '10-15 years'}</t>
+          <t>10-15 years</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'15-20_years'}</t>
+          <t>15-20_years</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '15-20 years'}</t>
+          <t>15-20 years</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'20-25_years'}</t>
+          <t>20-25_years</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '20-25 years'}</t>
+          <t>20-25 years</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'fixed'}</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Fixed'}</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'floating'}</t>
+          <t>floating</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Floating'}</t>
+          <t>Floating</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'adjustable'}</t>
+          <t>adjustable</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Adjustable'}</t>
+          <t>Adjustable</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'primary_residence'}</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Primary Residence'}</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'investment'}</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Investment'}</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'vacation'}</t>
+          <t>vacation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Vacation'}</t>
+          <t>Vacation</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'refinance'}</t>
+          <t>refinance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Refinance'}</t>
+          <t>Refinance</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'pre-approved'}</t>
+          <t>pre-approved</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Pre-Approved'}</t>
+          <t>Pre-Approved</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'primary_residence'}</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Primary Residence'}</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'investment'}</t>
+          <t>investment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Investment'}</t>
+          <t>Investment</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'vacation'}</t>
+          <t>vacation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Vacation'}</t>
+          <t>Vacation</t>
         </is>
       </c>
     </row>
